--- a/株式会社あらうち御中_LINEOA施策提案【SIM】ver1.3.xlsx
+++ b/株式会社あらうち御中_LINEOA施策提案【SIM】ver1.3.xlsx
@@ -3226,7 +3226,7 @@
         <v>194</v>
       </c>
       <c r="B2" s="157">
-        <v>46269</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3866,22 +3866,22 @@
         <v>22</v>
       </c>
       <c r="E22" s="63">
-        <f>IF(E17=FALSE,0,E71/$P$30)</f>
+        <v>0</v>
       </c>
       <c r="F22" s="63">
-        <f>IF(F17=FALSE,0,F71/$P$30)</f>
+        <v>0</v>
       </c>
       <c r="G22" s="63">
-        <f>IF(G17=FALSE,0,G71/$P$30)</f>
+        <v>0</v>
       </c>
       <c r="H22" s="63">
-        <f>IF(H17=FALSE,0,H71/$P$30)</f>
+        <v>0</v>
       </c>
       <c r="I22" s="63">
-        <f>IF(I17=FALSE,0,I71/$P$30)</f>
+        <v>0</v>
       </c>
       <c r="J22" s="63">
-        <f>IF(J17=FALSE,0,J71/$P$30)</f>
+        <v>0</v>
       </c>
       <c r="K22" s="11"/>
       <c r="L22" s="7"/>
@@ -3933,7 +3933,7 @@
       <c r="L23" s="7"/>
       <c r="N23" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">離脱防止＝UU×表示55%×クリック12%×追加12%（FMTの式）</t>
+          <t xml:space="preserve">離脱防止＝UU×表示55%×クリック12%×追加12%（FMTの式）。3か月目以降は前月の1.01倍（FMTの式）</t>
         </is>
       </c>
       <c r="O23" s="17" t="s">
@@ -3982,7 +3982,7 @@
       <c r="L24" s="7"/>
       <c r="N24" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">サンクスLINE＝フォームの問い合わせ×15%（到達×情報一致70%前後×追加。FMTの式）</t>
+          <t xml:space="preserve">サンクスLINE＝フォームの問い合わせ×15%（FMTの式）。2か月目以降は前月の1.01倍。経由した方はCV①に数えない</t>
         </is>
       </c>
       <c r="O24" s="22" t="s">
@@ -4071,8 +4071,10 @@
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
-      <c r="N26" s="72" t="s">
-        <v>143</v>
+      <c r="N26" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイトのLINEボタン＝UU×0.5%（FMTのP15）＝月約9人。リンク先を友だち追加URLに差し替える前提</t>
+        </is>
       </c>
       <c r="O26" s="17" t="s">
         <v>42</v>
@@ -4117,7 +4119,7 @@
       <c r="L27" s="7"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ブロック率：現状35%（仮置き）から月1%ずつ上昇（用済み型。友だち追加広告の流入が無いので上げ幅は小さい）</t>
+          <t xml:space="preserve">ブロック率：現状35%（仮置き）から前月の1.01倍ずつ上昇（6か月目で37%。用済み型。友だち追加広告の流入が無いので上げ幅は小さい）</t>
         </is>
       </c>
       <c r="O27" s="17" t="s">
@@ -4288,6 +4290,11 @@
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">企画配信：有効な友だち×80%（FMT）。4か月目からは反応しない方・問い合わせ済みの方を外して、さらに8割に絞る想定（FMTのQ24）</t>
+        </is>
+      </c>
       <c r="S31" s="34"/>
       <c r="U31" s="34"/>
       <c r="W31" s="34"/>
@@ -4323,8 +4330,10 @@
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
-      <c r="N32" s="69" t="s">
-        <v>157</v>
+      <c r="N32" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ステップ配信10通（サイト経由・サンクスLINE経由で各10通。企画案の表2）</t>
+        </is>
       </c>
       <c r="O32" s="17" t="s">
         <v>146</v>
@@ -4350,25 +4359,30 @@
         <v>0</v>
       </c>
       <c r="E33" s="63">
-        <f>+E29*E32*$P$26*$P$27*$P$28*$P$36</f>
+        <f>+E26*E32*$P$26*$P$27*$P$36</f>
       </c>
       <c r="F33" s="63">
-        <f t="shared" ref="F33:G33" si="10">+F29*F32*$P$26*$P$27*$P$28*$P$36</f>
+        <f>+F26*F32*$P$26*$P$27*$P$36</f>
       </c>
       <c r="G33" s="63">
-        <f t="shared" si="10"/>
+        <f>+G26*G32*$P$26*$P$27*$P$36</f>
       </c>
       <c r="H33" s="63">
-        <f>+H29*H32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <f>+H26*H32*$P$26*$P$27*$P$36</f>
       </c>
       <c r="I33" s="63">
-        <f t="shared" ref="I33:J33" si="11">+I29*I32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <f>+I26*I32*$P$26*$P$27*$P$36</f>
       </c>
       <c r="J33" s="63">
-        <f t="shared" si="11"/>
+        <f>+J26*J32*$P$26*$P$27*$P$36</f>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ステップ配信の対象＝その月の新しい友だち（開始条件＝友だち追加）。FMTの「ターゲット数×20%」は使わない</t>
+        </is>
+      </c>
       <c r="O33" s="17" t="s">
         <v>160</v>
       </c>
@@ -4389,22 +4403,22 @@
         <f>+D29*D30</f>
       </c>
       <c r="E34" s="46">
-        <f>+E29*E30*$P$24+E29*E32*$P$28</f>
+        <f>+E29*E30*$P$24+E26*E32</f>
       </c>
       <c r="F34" s="46">
-        <f>+F29*F30*$P$24+F29*F32*$P$28</f>
+        <f>+F29*F30*$P$24+F26*F32</f>
       </c>
       <c r="G34" s="46">
-        <f>+G29*G30*$P$24+G29*G32*$P$28</f>
+        <f>+G29*G30*$P$24+G26*G32</f>
       </c>
       <c r="H34" s="46">
-        <f>+H29*H30*$P$24*$Q$24+H29*H32*$P$28*$Q$28</f>
+        <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
       </c>
       <c r="I34" s="46">
-        <f>+I29*I30*$P$24*$Q$24+I29*I32*$P$28*$Q$28</f>
+        <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
       </c>
       <c r="J34" s="46">
-        <f>+J29*J30*$P$24*$Q$24+J29*J32*$P$28*$Q$28</f>
+        <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -4412,7 +4426,7 @@
         <v>161</v>
       </c>
       <c r="P34" s="75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="12"/>
@@ -4794,6 +4808,11 @@
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">友だち獲得単価＝離脱防止＋サンクスLINEの月額÷増えた友だち（無料のサイトのボタン経由も含む）</t>
+        </is>
+      </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A47" s="120" t="s">
@@ -5316,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="51">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="33">IF(E34&lt;5000,5000,15000)</f>
@@ -5336,8 +5355,10 @@
       <c r="J68" s="28">
         <f t="shared" si="33"/>
       </c>
-      <c r="N68" s="69" t="s">
-        <v>155</v>
+      <c r="N68" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">アカウント費：配信5,000通未満は月5,000円（FMTの式）。初期は0（アカウントは既にある）</t>
+        </is>
       </c>
       <c r="O68" s="17" t="s">
         <v>154</v>
@@ -5494,22 +5515,22 @@
         <f>SUM(D65:D72)</f>
       </c>
       <c r="E73" s="114">
-        <f t="shared" ref="E73" si="34">SUM(E65:E72)</f>
+        <f>SUM(E65:E72)+E54</f>
       </c>
       <c r="F73" s="114">
-        <f t="shared" ref="F73" si="35">SUM(F65:F72)</f>
+        <f>SUM(F65:F72)+F54</f>
       </c>
       <c r="G73" s="114">
-        <f t="shared" ref="G73" si="36">SUM(G65:G72)</f>
+        <f>SUM(G65:G72)+G54</f>
       </c>
       <c r="H73" s="114">
-        <f t="shared" ref="H73" si="37">SUM(H65:H72)</f>
+        <f>SUM(H65:H72)+H54</f>
       </c>
       <c r="I73" s="114">
-        <f t="shared" ref="I73" si="38">SUM(I65:I72)</f>
+        <f>SUM(I65:I72)+I54</f>
       </c>
       <c r="J73" s="114">
-        <f t="shared" ref="J73" si="39">SUM(J65:J72)</f>
+        <f>SUM(J65:J72)+J54</f>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.4">
@@ -5830,10 +5851,10 @@
         <f>+'SIM_離脱防止＋サンクスLINE'!D16</f>
       </c>
       <c r="D15" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!E16</f>
+        <f>+'SIM_離脱防止＋サンクスLINE'!G16</f>
       </c>
       <c r="E15" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!F16</f>
+        <f>+'SIM_離脱防止＋サンクスLINE'!J16</f>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -5944,8 +5965,10 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A19" s="85" t="s">
-        <v>94</v>
+      <c r="A19" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
@@ -5965,8 +5988,10 @@
       <c r="Y19" s="35"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A20" s="85" t="s">
-        <v>93</v>
+      <c r="A20" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="87">
@@ -6059,13 +6084,13 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="10">
-        <f>15000+C29*C30</f>
+        <f>+'SIM_離脱防止＋サンクスLINE'!E68+C29*C30</f>
       </c>
       <c r="D25" s="10">
-        <f>15000+D29*D30</f>
+        <f>+'SIM_離脱防止＋サンクスLINE'!G68+D29*D30</f>
       </c>
       <c r="E25" s="10">
-        <f>15000+E29*E30</f>
+        <f>+'SIM_離脱防止＋サンクスLINE'!J68+E29*E30</f>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
